--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>226</v>
+        <v>382</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E2">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="D3">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E3">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>382</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>426</v>
